--- a/docs/snapshot-fact-tags.xlsx
+++ b/docs/snapshot-fact-tags.xlsx
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>enum: payroll | transfer_own | gift | loan_proceeds | refund | interest | fee | vendor | unknown</t>
+          <t>enum: payroll | transfer_own | transfer_third_party_in | transfer_third_party_out | debt_payment | gift | loan_proceeds | refund | interest | fee | vendor | unknown</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">

--- a/docs/snapshot-fact-tags.xlsx
+++ b/docs/snapshot-fact-tags.xlsx
@@ -5721,7 +5721,7 @@
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>AI-at-rule-time</t>
+          <t>Deterministic</t>
         </is>
       </c>
     </row>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>Condo master + fidelity policy adequacy.</t>
+          <t>Condo master policy adequacy (presence, replacement-cost basis, general liability limit). Fidelity/crime (B7-4-02) is deliberately NOT evaluated — its unit-count input never resolves.</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>AI-at-rule-time</t>
+          <t>Deterministic</t>
         </is>
       </c>
     </row>

--- a/docs/snapshot-fact-tags.xlsx
+++ b/docs/snapshot-fact-tags.xlsx
@@ -7938,7 +7938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8323,11 +8323,11 @@
         </is>
       </c>
       <c r="B20" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>property.is_warrantable_condo</t>
+          <t>condo.questionnaire_present, property.type</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
@@ -9423,11 +9423,11 @@
         </is>
       </c>
       <c r="B75" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>housing.mi_monthly, loan.amount, property.appraised_value, mi.required</t>
+          <t>loan.ltv_percent, program.type</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
@@ -10093,6 +10093,26 @@
       <c r="D108" s="14" t="inlineStr">
         <is>
           <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MI-4</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>mi.fha_ufmip_percent, program.type</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Deterministic</t>
         </is>
       </c>
     </row>

--- a/docs/snapshot-fact-tags.xlsx
+++ b/docs/snapshot-fact-tags.xlsx
@@ -7938,7 +7938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>liab.is_derogatory, liab.derogatory_type, liab.derogatory_date</t>
+          <t>credit.derogatory_months_elapsed, liab.derogatory_type, liab.is_derogatory</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
@@ -8523,11 +8523,11 @@
         </is>
       </c>
       <c r="B30" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>liab.is_derogatory, liab.payment_status</t>
+          <t>liab.is_mortgage, liab.mortgage_late_60_plus_last_12mo, liab.payment_status, liab.structured_history_confident</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
@@ -8563,11 +8563,11 @@
         </is>
       </c>
       <c r="B32" s="20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>liab.balance, liab.derogatory_type</t>
+          <t>credit.collection_aggregate_balance, credit.has_collections, credit.largest_single_collection_balance, program.type, property.occupancy, property.type</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -10113,6 +10113,26 @@
       <c r="D109" t="inlineStr">
         <is>
           <t>Deterministic</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>CR-5</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>credit.inquiry_explained</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Mixed / AI-assisted</t>
         </is>
       </c>
     </row>

--- a/docs/snapshot-fact-tags.xlsx
+++ b/docs/snapshot-fact-tags.xlsx
@@ -9987,7 +9987,7 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>title.parties_match</t>
+          <t>title.vested_owner_matches</t>
         </is>
       </c>
       <c r="D103" s="14" t="inlineStr">
@@ -10003,11 +10003,11 @@
         </is>
       </c>
       <c r="B104" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104" s="21" t="inlineStr">
         <is>
-          <t>title.legal_desc_matches</t>
+          <t>title.legal_description, title.property_address</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
@@ -10083,11 +10083,11 @@
         </is>
       </c>
       <c r="B108" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C108" s="21" t="inlineStr">
         <is>
-          <t>title.rapid_transfer</t>
+          <t>title.chain_has_gap, title.chain_shortest_interval_days, title.chain_transfer_count</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">

--- a/docs/snapshot-fact-tags.xlsx
+++ b/docs/snapshot-fact-tags.xlsx
@@ -6131,12 +6131,12 @@
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>enum: yes | no + list</t>
+          <t>enum: yes | no | unknown</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>Personal property included that may inflate value.</t>
+          <t>Does the contract include personal property that may inflate the price? yes | no | unknown (unknown when the contract does not say).</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">

--- a/docs/snapshot-fact-tags.xlsx
+++ b/docs/snapshot-fact-tags.xlsx
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>enum: yes | no</t>
+          <t>enum: yes | no | unknown</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>enum: yes | no | partial</t>
+          <t>enum: yes | no | partial | unknown</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>enum: yes | no</t>
+          <t>enum: yes | no | unknown</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>enum: complete | incomplete</t>
+          <t>enum: complete | incomplete | unknown</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">

--- a/docs/snapshot-fact-tags.xlsx
+++ b/docs/snapshot-fact-tags.xlsx
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>enum: yes | no + detail</t>
+          <t>enum: yes | no | unknown</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">

--- a/docs/snapshot-fact-tags.xlsx
+++ b/docs/snapshot-fact-tags.xlsx
@@ -2464,7 +2464,7 @@
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>AS-1, AS-7, AS-8, AS-12</t>
+          <t>AS-1, AS-2, AS-7, AS-8, AS-12</t>
         </is>
       </c>
       <c r="G4" s="13" t="inlineStr">
@@ -8003,11 +8003,11 @@
         </is>
       </c>
       <c r="B4" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>txn.apparent_category, txn.has_identified_source, txn.counterparty, contract.emd_amount, contract.emd_sourced</t>
+          <t>txn.apparent_category, txn.has_identified_source, txn.counterparty, contract.emd_amount, contract.emd_sourced, txn.is_money_in</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
